--- a/uploads/uploaded_weekly.xlsx
+++ b/uploads/uploaded_weekly.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Location</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Observed By</t>
+    <t>Raised By</t>
   </si>
   <si>
     <t>Area A</t>
@@ -52,6 +52,9 @@
     <t>Area D</t>
   </si>
   <si>
+    <t>Area E</t>
+  </si>
+  <si>
     <t>Obs 1</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>Obs 4</t>
   </si>
   <si>
+    <t>Obs 5</t>
+  </si>
+  <si>
     <t>Rec 1</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>Rec 4</t>
   </si>
   <si>
+    <t>Rec 5</t>
+  </si>
+  <si>
     <t>Worker 1</t>
   </si>
   <si>
@@ -88,6 +97,9 @@
     <t>Worker 4</t>
   </si>
   <si>
+    <t>Worker 5</t>
+  </si>
+  <si>
     <t>01/09/2026</t>
   </si>
   <si>
@@ -100,6 +112,9 @@
     <t>04/09/2026</t>
   </si>
   <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
@@ -109,12 +124,12 @@
     <t>High</t>
   </si>
   <si>
+    <t>Open</t>
+  </si>
+  <si>
     <t>Closed</t>
   </si>
   <si>
-    <t>Open</t>
-  </si>
-  <si>
     <t>Safety A</t>
   </si>
   <si>
@@ -125,6 +140,9 @@
   </si>
   <si>
     <t>Safety D</t>
+  </si>
+  <si>
+    <t>Safety E</t>
   </si>
 </sst>
 </file>
@@ -456,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -490,25 +508,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -516,25 +534,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -542,25 +560,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -568,25 +586,51 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="F5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
         <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/uploaded_weekly.xlsx
+++ b/uploads/uploaded_weekly.xlsx
@@ -14,18 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Observation</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Action By</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Finding</t>
+  </si>
+  <si>
+    <t>Corrective Action</t>
+  </si>
+  <si>
+    <t>Assignee</t>
   </si>
   <si>
     <t>Due Date</t>
@@ -40,109 +40,91 @@
     <t>Raised By</t>
   </si>
   <si>
-    <t>Area A</t>
-  </si>
-  <si>
-    <t>Area B</t>
-  </si>
-  <si>
-    <t>Area C</t>
-  </si>
-  <si>
-    <t>Area D</t>
-  </si>
-  <si>
-    <t>Area E</t>
-  </si>
-  <si>
-    <t>Obs 1</t>
-  </si>
-  <si>
-    <t>Obs 2</t>
-  </si>
-  <si>
-    <t>Obs 3</t>
-  </si>
-  <si>
-    <t>Obs 4</t>
-  </si>
-  <si>
-    <t>Obs 5</t>
-  </si>
-  <si>
-    <t>Rec 1</t>
-  </si>
-  <si>
-    <t>Rec 2</t>
-  </si>
-  <si>
-    <t>Rec 3</t>
-  </si>
-  <si>
-    <t>Rec 4</t>
-  </si>
-  <si>
-    <t>Rec 5</t>
-  </si>
-  <si>
-    <t>Worker 1</t>
-  </si>
-  <si>
-    <t>Worker 2</t>
-  </si>
-  <si>
-    <t>Worker 3</t>
-  </si>
-  <si>
-    <t>Worker 4</t>
-  </si>
-  <si>
-    <t>Worker 5</t>
-  </si>
-  <si>
-    <t>01/09/2026</t>
-  </si>
-  <si>
-    <t>02/09/2026</t>
-  </si>
-  <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>05/09/2026</t>
+    <t>Area 1</t>
+  </si>
+  <si>
+    <t>Area 2</t>
+  </si>
+  <si>
+    <t>Area 3</t>
+  </si>
+  <si>
+    <t>Area 4</t>
+  </si>
+  <si>
+    <t>Finding A</t>
+  </si>
+  <si>
+    <t>Finding B</t>
+  </si>
+  <si>
+    <t>Finding C</t>
+  </si>
+  <si>
+    <t>Finding D</t>
+  </si>
+  <si>
+    <t>Action A</t>
+  </si>
+  <si>
+    <t>Action B</t>
+  </si>
+  <si>
+    <t>Action C</t>
+  </si>
+  <si>
+    <t>Action D</t>
+  </si>
+  <si>
+    <t>User A</t>
+  </si>
+  <si>
+    <t>User B</t>
+  </si>
+  <si>
+    <t>User C</t>
+  </si>
+  <si>
+    <t>User D</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
+    <t>High</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
     <t>Closed</t>
   </si>
   <si>
-    <t>Safety A</t>
-  </si>
-  <si>
-    <t>Safety B</t>
-  </si>
-  <si>
-    <t>Safety C</t>
-  </si>
-  <si>
-    <t>Safety D</t>
-  </si>
-  <si>
-    <t>Safety E</t>
+    <t>Officer 1</t>
+  </si>
+  <si>
+    <t>Officer 2</t>
+  </si>
+  <si>
+    <t>Officer 3</t>
+  </si>
+  <si>
+    <t>Officer 4</t>
   </si>
 </sst>
 </file>
@@ -474,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -508,25 +490,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
         <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -534,25 +516,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
         <v>29</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
         <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -560,25 +542,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
         <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -586,51 +568,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
